--- a/thread-strength/03_analyses/assemble-thread-summary/thread-summary-trossulus.xlsx
+++ b/thread-strength/03_analyses/assemble-thread-summary/thread-summary-trossulus.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="376">
   <si>
     <t xml:space="preserve">sort_ID</t>
   </si>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">rna_sequenced</t>
   </si>
   <si>
-    <t xml:space="preserve">T01_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T01</t>
+    <t xml:space="preserve">T001_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T001</t>
   </si>
   <si>
     <t xml:space="preserve"/>
@@ -86,136 +86,136 @@
     <t xml:space="preserve">yes</t>
   </si>
   <si>
-    <t xml:space="preserve">T01_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T01_3</t>
+    <t xml:space="preserve">T001_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T001_3</t>
   </si>
   <si>
     <t xml:space="preserve">tearing</t>
   </si>
   <si>
-    <t xml:space="preserve">T02_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T02_2</t>
+    <t xml:space="preserve">T002_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T002_2</t>
   </si>
   <si>
     <t xml:space="preserve">cohesive</t>
   </si>
   <si>
-    <t xml:space="preserve">T02_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T03_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T03</t>
+    <t xml:space="preserve">T002_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T003_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T003</t>
   </si>
   <si>
     <t xml:space="preserve">pealing</t>
   </si>
   <si>
-    <t xml:space="preserve">T03_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T03_3</t>
+    <t xml:space="preserve">T003_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T003_3</t>
   </si>
   <si>
     <t xml:space="preserve">near edge</t>
   </si>
   <si>
-    <t xml:space="preserve">T04_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T04_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T05_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T05_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T05_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T06_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T06_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T06_3</t>
+    <t xml:space="preserve">T004_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T004_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T004_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T005_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T005_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T005_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T006_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T006_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T006_3</t>
   </si>
   <si>
     <t xml:space="preserve">close to another</t>
   </si>
   <si>
-    <t xml:space="preserve">T08_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T08</t>
+    <t xml:space="preserve">T008_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T008</t>
   </si>
   <si>
     <t xml:space="preserve">note: its possible I cleaned the sample to harshly</t>
   </si>
   <si>
-    <t xml:space="preserve">T08_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T08_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T09_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T09_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T09_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T10_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T10_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T10_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T11_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T11_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T11_3</t>
+    <t xml:space="preserve">T008_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T008_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T009_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T009_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T009_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T010_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T010_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T010_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T011_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T011_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T011_3</t>
   </si>
   <si>
     <t xml:space="preserve">thread at 0.255 N. thread again at 0.19 N</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">try2</t>
   </si>
   <si>
-    <t xml:space="preserve">T11_4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T12_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T12_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T12_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T13_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T13</t>
+    <t xml:space="preserve">T011_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T012_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T012_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T012_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T013_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T013</t>
   </si>
   <si>
     <t xml:space="preserve">OA</t>
@@ -251,13 +251,7 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">T13_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T14_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T14</t>
+    <t xml:space="preserve">T013_3</t>
   </si>
   <si>
     <t xml:space="preserve">T014_1</t>
@@ -266,16 +260,10 @@
     <t xml:space="preserve">T014</t>
   </si>
   <si>
-    <t xml:space="preserve">T14_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T14_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T15_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T15</t>
+    <t xml:space="preserve">T014_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T014_3</t>
   </si>
   <si>
     <t xml:space="preserve">T015_1</t>
@@ -284,16 +272,10 @@
     <t xml:space="preserve">T015</t>
   </si>
   <si>
-    <t xml:space="preserve">T15_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T15_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T16_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T16</t>
+    <t xml:space="preserve">T015_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T015_3</t>
   </si>
   <si>
     <t xml:space="preserve">T016_1</t>
@@ -302,61 +284,37 @@
     <t xml:space="preserve">T016</t>
   </si>
   <si>
-    <t xml:space="preserve">T16_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T016_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T16_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T016_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T17_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T17</t>
-  </si>
-  <si>
     <t xml:space="preserve">T017_1</t>
   </si>
   <si>
     <t xml:space="preserve">T017</t>
   </si>
   <si>
-    <t xml:space="preserve">T17_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T017_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T17_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T017_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T18_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T18_2</t>
+    <t xml:space="preserve">T018_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T018_2</t>
   </si>
   <si>
     <t xml:space="preserve">thread at 0.265 N</t>
   </si>
   <si>
-    <t xml:space="preserve">T18_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T19_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T19</t>
+    <t xml:space="preserve">T018_3</t>
   </si>
   <si>
     <t xml:space="preserve">T019_1</t>
@@ -365,28 +323,22 @@
     <t xml:space="preserve">T019</t>
   </si>
   <si>
-    <t xml:space="preserve">T19_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T019_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T19_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T019_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T20_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T20_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T20_3</t>
+    <t xml:space="preserve">T020_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T020_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T020_3</t>
   </si>
   <si>
     <t xml:space="preserve">T021_1</t>
@@ -395,28 +347,22 @@
     <t xml:space="preserve">T021</t>
   </si>
   <si>
-    <t xml:space="preserve">T22_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T22</t>
+    <t xml:space="preserve">T022_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T022</t>
   </si>
   <si>
     <t xml:space="preserve">Scrap</t>
   </si>
   <si>
-    <t xml:space="preserve">T22_2</t>
+    <t xml:space="preserve">T022_2</t>
   </si>
   <si>
     <t xml:space="preserve">also pulled off another nearby</t>
   </si>
   <si>
-    <t xml:space="preserve">T22_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T23_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T23</t>
+    <t xml:space="preserve">T022_3</t>
   </si>
   <si>
     <t xml:space="preserve">T023_1</t>
@@ -425,37 +371,25 @@
     <t xml:space="preserve">T023</t>
   </si>
   <si>
-    <t xml:space="preserve">T23_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T023_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T23_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T023_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T24_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T24</t>
+    <t xml:space="preserve">T024_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T024</t>
   </si>
   <si>
     <t xml:space="preserve">thread at 0.39. grabbed remainder and retested. thread again at .225</t>
   </si>
   <si>
-    <t xml:space="preserve">T24_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T24_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T25_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T25</t>
+    <t xml:space="preserve">T024_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T024_3</t>
   </si>
   <si>
     <t xml:space="preserve">T025_1</t>
@@ -464,70 +398,40 @@
     <t xml:space="preserve">T025</t>
   </si>
   <si>
-    <t xml:space="preserve">T25_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T025_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T25_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T025_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T26_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T26</t>
-  </si>
-  <si>
     <t xml:space="preserve">T026_1</t>
   </si>
   <si>
     <t xml:space="preserve">T026</t>
   </si>
   <si>
-    <t xml:space="preserve">T26_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T026_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T26_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T026_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T27_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T27</t>
-  </si>
-  <si>
     <t xml:space="preserve">T027_1</t>
   </si>
   <si>
     <t xml:space="preserve">T027</t>
   </si>
   <si>
-    <t xml:space="preserve">T27_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T027_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T27_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T027_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T28_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T28</t>
+    <t xml:space="preserve">T028_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T028</t>
   </si>
   <si>
     <t xml:space="preserve">OW</t>
@@ -536,24 +440,18 @@
     <t xml:space="preserve">thread at 0.085</t>
   </si>
   <si>
-    <t xml:space="preserve">T28_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T28_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T28_4</t>
+    <t xml:space="preserve">T028_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T028_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T028_4</t>
   </si>
   <si>
     <t xml:space="preserve">threat at 0.415 N</t>
   </si>
   <si>
-    <t xml:space="preserve">T29_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T29</t>
-  </si>
-  <si>
     <t xml:space="preserve">T029_1</t>
   </si>
   <si>
@@ -563,27 +461,15 @@
     <t xml:space="preserve">1-3 were close to eachother with little overlap.</t>
   </si>
   <si>
-    <t xml:space="preserve">T29_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T029_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T29_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T029_3</t>
   </si>
   <si>
     <t xml:space="preserve">T029_4</t>
   </si>
   <si>
-    <t xml:space="preserve">T30_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T30</t>
-  </si>
-  <si>
     <t xml:space="preserve">T030_1</t>
   </si>
   <si>
@@ -596,67 +482,40 @@
     <t xml:space="preserve">T030_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T31_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T31</t>
-  </si>
-  <si>
     <t xml:space="preserve">T031_1</t>
   </si>
   <si>
     <t xml:space="preserve">T031</t>
   </si>
   <si>
-    <t xml:space="preserve">T31_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T031_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T31_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T031_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T32_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T32_3</t>
+    <t xml:space="preserve">T032_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T032_3</t>
   </si>
   <si>
     <t xml:space="preserve">Broke at 0.325, and retested</t>
   </si>
   <si>
-    <t xml:space="preserve">T33_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T33</t>
-  </si>
-  <si>
     <t xml:space="preserve">T033_1</t>
   </si>
   <si>
     <t xml:space="preserve">T033</t>
   </si>
   <si>
-    <t xml:space="preserve">T33_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T033_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T33_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T34_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T34</t>
+    <t xml:space="preserve">T033_3</t>
   </si>
   <si>
     <t xml:space="preserve">T034_1</t>
@@ -665,15 +524,9 @@
     <t xml:space="preserve">T034</t>
   </si>
   <si>
-    <t xml:space="preserve">T34_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T034_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T34_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T034_3</t>
   </si>
   <si>
@@ -686,142 +539,73 @@
     <t xml:space="preserve">T035_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T36_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T36</t>
-  </si>
-  <si>
     <t xml:space="preserve">T036_1</t>
   </si>
   <si>
     <t xml:space="preserve">T036</t>
   </si>
   <si>
-    <t xml:space="preserve">T36_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T036_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T36_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T036_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T37_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T37</t>
-  </si>
-  <si>
     <t xml:space="preserve">T037_1</t>
   </si>
   <si>
     <t xml:space="preserve">T037</t>
   </si>
   <si>
-    <t xml:space="preserve">T37_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T037_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T37_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T037_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T38_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T38</t>
-  </si>
-  <si>
     <t xml:space="preserve">T038_1</t>
   </si>
   <si>
     <t xml:space="preserve">T038</t>
   </si>
   <si>
-    <t xml:space="preserve">T38_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T038_2</t>
   </si>
   <si>
     <t xml:space="preserve">T038_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T39_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T39</t>
-  </si>
-  <si>
     <t xml:space="preserve">T039_1</t>
   </si>
   <si>
     <t xml:space="preserve">T039</t>
   </si>
   <si>
-    <t xml:space="preserve">T39_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T039_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T39_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T039_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T40_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T40</t>
-  </si>
-  <si>
     <t xml:space="preserve">T040_1</t>
   </si>
   <si>
     <t xml:space="preserve">T040</t>
   </si>
   <si>
-    <t xml:space="preserve">T40_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T040_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T40_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T040_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T41_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T41</t>
-  </si>
-  <si>
     <t xml:space="preserve">T041_1</t>
   </si>
   <si>
     <t xml:space="preserve">T041</t>
   </si>
   <si>
-    <t xml:space="preserve">T41_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T42_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T42</t>
+    <t xml:space="preserve">T041_2</t>
   </si>
   <si>
     <t xml:space="preserve">T042_1</t>
@@ -833,64 +617,52 @@
     <t xml:space="preserve">thread broke at .2350 N. grabbed remainter and tested again. thread broke again at .42 N.</t>
   </si>
   <si>
-    <t xml:space="preserve">T42_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T042_2</t>
   </si>
   <si>
     <t xml:space="preserve">pulled off mica</t>
   </si>
   <si>
-    <t xml:space="preserve">T42_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T042_3</t>
   </si>
   <si>
     <t xml:space="preserve">close overlap</t>
   </si>
   <si>
-    <t xml:space="preserve">T43_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T43</t>
+    <t xml:space="preserve">T043_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T043</t>
   </si>
   <si>
     <t xml:space="preserve">DO</t>
   </si>
   <si>
-    <t xml:space="preserve">T43_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T43_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T44_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T44_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T45_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T45_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T45_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T46_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T46</t>
+    <t xml:space="preserve">T043_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T043_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T044_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T044_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T045_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T045_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T045_3</t>
   </si>
   <si>
     <t xml:space="preserve">T046_1</t>
@@ -899,33 +671,21 @@
     <t xml:space="preserve">T046</t>
   </si>
   <si>
-    <t xml:space="preserve">T46_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T046_2</t>
   </si>
   <si>
     <t xml:space="preserve">T046_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T47_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T47_2</t>
+    <t xml:space="preserve">T047_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T047</t>
   </si>
   <si>
     <t xml:space="preserve">T047_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T47_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T047_3</t>
   </si>
   <si>
@@ -935,55 +695,40 @@
     <t xml:space="preserve">very close to another, pulled it off with it</t>
   </si>
   <si>
-    <t xml:space="preserve">T48_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T48_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T49_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T49_2</t>
+    <t xml:space="preserve">T048_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T048_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T049_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T049</t>
   </si>
   <si>
     <t xml:space="preserve">T049_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T49_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T049_3</t>
   </si>
   <si>
     <t xml:space="preserve">T049_4</t>
   </si>
   <si>
-    <t xml:space="preserve">T50_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T50_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T50_3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T51_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T51</t>
+    <t xml:space="preserve">T050_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T050_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T050_3</t>
   </si>
   <si>
     <t xml:space="preserve">T051_1</t>
@@ -992,49 +737,34 @@
     <t xml:space="preserve">T051</t>
   </si>
   <si>
-    <t xml:space="preserve">T52_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T52_2</t>
+    <t xml:space="preserve">T052_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T052</t>
   </si>
   <si>
     <t xml:space="preserve">T052_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T52_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T052_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T53_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T53_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T53_3</t>
+    <t xml:space="preserve">T053_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T053_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T053_3</t>
   </si>
   <si>
     <t xml:space="preserve">thread at 0.17</t>
   </si>
   <si>
-    <t xml:space="preserve">T53_5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T55_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T55</t>
+    <t xml:space="preserve">T053_5</t>
   </si>
   <si>
     <t xml:space="preserve">T055_1</t>
@@ -1043,66 +773,33 @@
     <t xml:space="preserve">T055</t>
   </si>
   <si>
-    <t xml:space="preserve">T55_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T055_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T56_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T56</t>
-  </si>
-  <si>
     <t xml:space="preserve">T056_1</t>
   </si>
   <si>
     <t xml:space="preserve">T056</t>
   </si>
   <si>
-    <t xml:space="preserve">T56_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T056_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T56_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T056_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T57_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T57</t>
-  </si>
-  <si>
     <t xml:space="preserve">T057_1</t>
   </si>
   <si>
     <t xml:space="preserve">T057</t>
   </si>
   <si>
-    <t xml:space="preserve">T57_2</t>
-  </si>
-  <si>
     <t xml:space="preserve">T057_2</t>
   </si>
   <si>
-    <t xml:space="preserve">T57_3</t>
-  </si>
-  <si>
     <t xml:space="preserve">T057_3</t>
   </si>
   <si>
-    <t xml:space="preserve">T58_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">T58</t>
-  </si>
-  <si>
     <t xml:space="preserve">T058_1</t>
   </si>
   <si>
@@ -1112,7 +809,7 @@
     <t xml:space="preserve">Close to the edge</t>
   </si>
   <si>
-    <t xml:space="preserve">T58_2</t>
+    <t xml:space="preserve">T058_2</t>
   </si>
   <si>
     <t xml:space="preserve">T089_1</t>
@@ -3772,10 +3469,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C40" t="n">
         <v>1</v>
@@ -3823,7 +3520,7 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
         <v>81</v>
@@ -3874,7 +3571,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B42" t="s">
         <v>81</v>
@@ -3925,10 +3622,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C43" t="n">
         <v>1</v>
@@ -3976,10 +3673,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C44" t="n">
         <v>1</v>
@@ -4027,10 +3724,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C45" t="n">
         <v>2</v>
@@ -4078,10 +3775,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B46" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C46" t="n">
         <v>3</v>
@@ -4129,10 +3826,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C47" t="n">
         <v>1</v>
@@ -4180,10 +3877,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B48" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -4231,10 +3928,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C49" t="n">
         <v>2</v>
@@ -4282,10 +3979,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C50" t="n">
         <v>2</v>
@@ -4333,10 +4030,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C51" t="n">
         <v>3</v>
@@ -4384,10 +4081,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C52" t="n">
         <v>3</v>
@@ -4435,10 +4132,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="B53" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C53" t="n">
         <v>1</v>
@@ -4486,10 +4183,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="B54" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
@@ -4537,10 +4234,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C55" t="n">
         <v>2</v>
@@ -4588,10 +4285,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C56" t="n">
         <v>2</v>
@@ -4639,10 +4336,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B57" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C57" t="n">
         <v>3</v>
@@ -4690,10 +4387,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="B58" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C58" t="n">
         <v>3</v>
@@ -4741,10 +4438,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
@@ -4792,10 +4489,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C60" t="n">
         <v>2</v>
@@ -4831,7 +4528,7 @@
       <c r="N60"/>
       <c r="O60"/>
       <c r="P60" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="Q60" t="s">
         <v>78</v>
@@ -4839,10 +4536,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="C61" t="n">
         <v>3</v>
@@ -4890,10 +4587,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="B62" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -4941,10 +4638,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -4992,10 +4689,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C64" t="n">
         <v>2</v>
@@ -5043,10 +4740,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C65" t="n">
         <v>2</v>
@@ -5094,10 +4791,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C66" t="n">
         <v>3</v>
@@ -5145,10 +4842,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C67" t="n">
         <v>3</v>
@@ -5196,10 +4893,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -5247,10 +4944,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C69" t="n">
         <v>2</v>
@@ -5298,10 +4995,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="B70" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C70" t="n">
         <v>3</v>
@@ -5349,10 +5046,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="C71" t="n">
         <v>1</v>
@@ -5400,10 +5097,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C72" t="n">
         <v>1</v>
@@ -5439,7 +5136,7 @@
       <c r="N72"/>
       <c r="O72"/>
       <c r="P72" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="Q72" t="s">
         <v>78</v>
@@ -5447,10 +5144,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
@@ -5492,7 +5189,7 @@
         <v>0</v>
       </c>
       <c r="P73" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="Q73" t="s">
         <v>78</v>
@@ -5500,10 +5197,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="C74" t="n">
         <v>3</v>
@@ -5551,10 +5248,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="B75" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C75" t="n">
         <v>1</v>
@@ -5602,10 +5299,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="B76" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
@@ -5653,10 +5350,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C77" t="n">
         <v>2</v>
@@ -5704,10 +5401,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B78" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C78" t="n">
         <v>2</v>
@@ -5755,10 +5452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="C79" t="n">
         <v>3</v>
@@ -5806,10 +5503,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B80" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C80" t="n">
         <v>3</v>
@@ -5857,10 +5554,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B81" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -5896,7 +5593,7 @@
       <c r="N81"/>
       <c r="O81"/>
       <c r="P81" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="Q81" t="s">
         <v>78</v>
@@ -5904,10 +5601,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -5943,7 +5640,7 @@
       <c r="N82"/>
       <c r="O82"/>
       <c r="P82" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="Q82" t="s">
         <v>78</v>
@@ -5951,10 +5648,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B83" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
@@ -6002,10 +5699,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="C84" t="n">
         <v>3</v>
@@ -6053,10 +5750,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B85" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C85" t="n">
         <v>1</v>
@@ -6104,10 +5801,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="B86" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -6155,10 +5852,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C87" t="n">
         <v>2</v>
@@ -6206,10 +5903,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>151</v>
+        <v>128</v>
       </c>
       <c r="B88" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C88" t="n">
         <v>2</v>
@@ -6257,10 +5954,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="B89" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C89" t="n">
         <v>3</v>
@@ -6308,10 +6005,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="B90" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C90" t="n">
         <v>3</v>
@@ -6359,10 +6056,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="B91" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -6410,10 +6107,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="B92" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -6461,10 +6158,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B93" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C93" t="n">
         <v>2</v>
@@ -6512,10 +6209,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="B94" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C94" t="n">
         <v>2</v>
@@ -6563,10 +6260,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="B95" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="C95" t="n">
         <v>3</v>
@@ -6614,10 +6311,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="B96" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="C96" t="n">
         <v>3</v>
@@ -6665,10 +6362,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="B97" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -6716,10 +6413,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -6767,10 +6464,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="B99" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C99" t="n">
         <v>2</v>
@@ -6818,10 +6515,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="C100" t="n">
         <v>2</v>
@@ -6869,10 +6566,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="B101" t="s">
-        <v>163</v>
+        <v>135</v>
       </c>
       <c r="C101" t="n">
         <v>3</v>
@@ -6920,10 +6617,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="C102" t="n">
         <v>3</v>
@@ -6971,10 +6668,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="B103" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -6992,7 +6689,7 @@
         <v>20</v>
       </c>
       <c r="H103" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I103" t="n">
         <v>0.085</v>
@@ -7010,7 +6707,7 @@
       <c r="N103"/>
       <c r="O103"/>
       <c r="P103" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="Q103" t="s">
         <v>78</v>
@@ -7018,10 +6715,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="B104" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C104" t="n">
         <v>2</v>
@@ -7039,7 +6736,7 @@
         <v>20</v>
       </c>
       <c r="H104" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I104" t="n">
         <v>0.185</v>
@@ -7069,10 +6766,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="B105" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C105" t="n">
         <v>3</v>
@@ -7090,7 +6787,7 @@
         <v>20</v>
       </c>
       <c r="H105" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I105" t="n">
         <v>0.17</v>
@@ -7120,10 +6817,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="C106" t="n">
         <v>4</v>
@@ -7141,7 +6838,7 @@
         <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I106" t="n">
         <v>0.415</v>
@@ -7159,7 +6856,7 @@
       <c r="N106"/>
       <c r="O106"/>
       <c r="P106" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="Q106" t="s">
         <v>78</v>
@@ -7167,10 +6864,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="B107" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C107" t="n">
         <v>1</v>
@@ -7188,7 +6885,7 @@
         <v>20</v>
       </c>
       <c r="H107" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I107" t="n">
         <v>0.445</v>
@@ -7218,10 +6915,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="B108" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
@@ -7236,10 +6933,10 @@
         <v>21</v>
       </c>
       <c r="G108" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H108" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I108" t="n">
         <v>0.1</v>
@@ -7263,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="Q108" t="s">
         <v>23</v>
@@ -7271,10 +6968,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="B109" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C109" t="n">
         <v>2</v>
@@ -7292,7 +6989,7 @@
         <v>20</v>
       </c>
       <c r="H109" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I109" t="n">
         <v>0.27</v>
@@ -7322,10 +7019,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B110" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C110" t="n">
         <v>2</v>
@@ -7340,10 +7037,10 @@
         <v>21</v>
       </c>
       <c r="G110" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H110" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I110" t="n">
         <v>0.13</v>
@@ -7373,10 +7070,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="B111" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="C111" t="n">
         <v>3</v>
@@ -7394,7 +7091,7 @@
         <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I111" t="n">
         <v>0.495</v>
@@ -7424,10 +7121,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="B112" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C112" t="n">
         <v>3</v>
@@ -7442,10 +7139,10 @@
         <v>21</v>
       </c>
       <c r="G112" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H112" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I112" t="n">
         <v>0.065</v>
@@ -7475,10 +7172,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="B113" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="C113" t="n">
         <v>4</v>
@@ -7493,10 +7190,10 @@
         <v>21</v>
       </c>
       <c r="G113" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H113" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I113" t="n">
         <v>0.11</v>
@@ -7526,10 +7223,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="B114" t="s">
-        <v>189</v>
+        <v>153</v>
       </c>
       <c r="C114" t="n">
         <v>1</v>
@@ -7547,7 +7244,7 @@
         <v>20</v>
       </c>
       <c r="H114" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I114" t="n">
         <v>0.43</v>
@@ -7577,10 +7274,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="B115" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -7595,10 +7292,10 @@
         <v>21</v>
       </c>
       <c r="G115" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H115" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I115" t="n">
         <v>0.2</v>
@@ -7628,10 +7325,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="B116" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="C116" t="n">
         <v>2</v>
@@ -7646,10 +7343,10 @@
         <v>21</v>
       </c>
       <c r="G116" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H116" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I116" t="n">
         <v>0.175</v>
@@ -7679,10 +7376,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="B117" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="C117" t="n">
         <v>3</v>
@@ -7697,10 +7394,10 @@
         <v>21</v>
       </c>
       <c r="G117" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H117" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I117" t="n">
         <v>0.265</v>
@@ -7730,10 +7427,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="B118" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
@@ -7751,7 +7448,7 @@
         <v>20</v>
       </c>
       <c r="H118" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I118" t="n">
         <v>0.155</v>
@@ -7781,10 +7478,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="B119" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
@@ -7799,10 +7496,10 @@
         <v>21</v>
       </c>
       <c r="G119" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H119" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I119" t="n">
         <v>0.205</v>
@@ -7832,10 +7529,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>198</v>
+        <v>158</v>
       </c>
       <c r="B120" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="C120" t="n">
         <v>2</v>
@@ -7853,7 +7550,7 @@
         <v>20</v>
       </c>
       <c r="H120" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I120" t="n">
         <v>0.275</v>
@@ -7883,10 +7580,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>199</v>
+        <v>158</v>
       </c>
       <c r="B121" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="C121" t="n">
         <v>2</v>
@@ -7901,10 +7598,10 @@
         <v>21</v>
       </c>
       <c r="G121" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H121" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I121" t="n">
         <v>0.15</v>
@@ -7934,10 +7631,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>200</v>
+        <v>159</v>
       </c>
       <c r="B122" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="C122" t="n">
         <v>3</v>
@@ -7955,7 +7652,7 @@
         <v>20</v>
       </c>
       <c r="H122" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I122" t="n">
         <v>0.325</v>
@@ -7985,10 +7682,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="B123" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="C123" t="n">
         <v>3</v>
@@ -8003,10 +7700,10 @@
         <v>21</v>
       </c>
       <c r="G123" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H123" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I123" t="n">
         <v>0.115</v>
@@ -8036,10 +7733,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="B124" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="C124" t="n">
         <v>2</v>
@@ -8057,7 +7754,7 @@
         <v>20</v>
       </c>
       <c r="H124" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I124" t="n">
         <v>0.25</v>
@@ -8087,10 +7784,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="B125" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="C125" t="n">
         <v>3</v>
@@ -8108,7 +7805,7 @@
         <v>20</v>
       </c>
       <c r="H125" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I125" t="n">
         <v>0.35</v>
@@ -8132,7 +7829,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="Q125" t="s">
         <v>78</v>
@@ -8140,10 +7837,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>206</v>
+        <v>164</v>
       </c>
       <c r="B126" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -8161,7 +7858,7 @@
         <v>20</v>
       </c>
       <c r="H126" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I126" t="n">
         <v>0.245</v>
@@ -8191,10 +7888,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>208</v>
+        <v>164</v>
       </c>
       <c r="B127" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="C127" t="n">
         <v>1</v>
@@ -8209,10 +7906,10 @@
         <v>21</v>
       </c>
       <c r="G127" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H127" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I127" t="n">
         <v>0.225</v>
@@ -8242,10 +7939,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="B128" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="C128" t="n">
         <v>2</v>
@@ -8263,7 +7960,7 @@
         <v>20</v>
       </c>
       <c r="H128" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I128" t="n">
         <v>0.365</v>
@@ -8293,10 +7990,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="B129" t="s">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="C129" t="n">
         <v>2</v>
@@ -8311,10 +8008,10 @@
         <v>21</v>
       </c>
       <c r="G129" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H129" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I129" t="n">
         <v>0.135</v>
@@ -8344,10 +8041,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="B130" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="C130" t="n">
         <v>3</v>
@@ -8365,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="H130" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I130" t="n">
         <v>0.255</v>
@@ -8395,10 +8092,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="B131" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="C131" t="n">
         <v>1</v>
@@ -8416,7 +8113,7 @@
         <v>20</v>
       </c>
       <c r="H131" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I131" t="n">
         <v>0.3</v>
@@ -8446,10 +8143,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="B132" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C132" t="n">
         <v>1</v>
@@ -8464,10 +8161,10 @@
         <v>21</v>
       </c>
       <c r="G132" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H132" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I132" t="n">
         <v>0.18</v>
@@ -8497,10 +8194,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="B133" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="C133" t="n">
         <v>2</v>
@@ -8518,7 +8215,7 @@
         <v>20</v>
       </c>
       <c r="H133" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I133" t="n">
         <v>0.235</v>
@@ -8548,10 +8245,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>218</v>
+        <v>170</v>
       </c>
       <c r="B134" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C134" t="n">
         <v>2</v>
@@ -8566,10 +8263,10 @@
         <v>21</v>
       </c>
       <c r="G134" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H134" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I134" t="n">
         <v>0.105</v>
@@ -8599,10 +8296,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>219</v>
+        <v>171</v>
       </c>
       <c r="B135" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="C135" t="n">
         <v>3</v>
@@ -8620,7 +8317,7 @@
         <v>20</v>
       </c>
       <c r="H135" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I135" t="n">
         <v>0.235</v>
@@ -8650,10 +8347,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="B136" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="C136" t="n">
         <v>3</v>
@@ -8668,10 +8365,10 @@
         <v>21</v>
       </c>
       <c r="G136" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H136" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I136" t="n">
         <v>0.125</v>
@@ -8701,10 +8398,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="B137" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="C137" t="n">
         <v>1</v>
@@ -8719,10 +8416,10 @@
         <v>21</v>
       </c>
       <c r="G137" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H137" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I137" t="n">
         <v>0.125</v>
@@ -8752,10 +8449,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="B138" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="C138" t="n">
         <v>2</v>
@@ -8770,10 +8467,10 @@
         <v>21</v>
       </c>
       <c r="G138" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H138" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I138" t="n">
         <v>0.08</v>
@@ -8803,10 +8500,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="B139" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="C139" t="n">
         <v>1</v>
@@ -8824,7 +8521,7 @@
         <v>20</v>
       </c>
       <c r="H139" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I139" t="n">
         <v>0.1</v>
@@ -8854,10 +8551,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="B140" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -8872,10 +8569,10 @@
         <v>21</v>
       </c>
       <c r="G140" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H140" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I140" t="n">
         <v>0.235</v>
@@ -8905,10 +8602,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>228</v>
+        <v>177</v>
       </c>
       <c r="B141" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="C141" t="n">
         <v>2</v>
@@ -8926,7 +8623,7 @@
         <v>20</v>
       </c>
       <c r="H141" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I141" t="n">
         <v>0.6</v>
@@ -8956,10 +8653,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>229</v>
+        <v>177</v>
       </c>
       <c r="B142" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="C142" t="n">
         <v>2</v>
@@ -8974,10 +8671,10 @@
         <v>21</v>
       </c>
       <c r="G142" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H142" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I142" t="n">
         <v>0.215</v>
@@ -9007,10 +8704,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="B143" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="C143" t="n">
         <v>3</v>
@@ -9028,7 +8725,7 @@
         <v>20</v>
       </c>
       <c r="H143" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I143" t="n">
         <v>0.27</v>
@@ -9058,10 +8755,10 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>231</v>
+        <v>178</v>
       </c>
       <c r="B144" t="s">
-        <v>227</v>
+        <v>176</v>
       </c>
       <c r="C144" t="n">
         <v>3</v>
@@ -9076,10 +8773,10 @@
         <v>21</v>
       </c>
       <c r="G144" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H144" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I144" t="n">
         <v>0.165</v>
@@ -9109,10 +8806,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>232</v>
+        <v>179</v>
       </c>
       <c r="B145" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="C145" t="n">
         <v>1</v>
@@ -9130,7 +8827,7 @@
         <v>20</v>
       </c>
       <c r="H145" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I145" t="n">
         <v>0.19</v>
@@ -9160,10 +8857,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="B146" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="C146" t="n">
         <v>1</v>
@@ -9178,10 +8875,10 @@
         <v>21</v>
       </c>
       <c r="G146" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H146" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I146" t="n">
         <v>0.335</v>
@@ -9211,10 +8908,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="B147" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="C147" t="n">
         <v>2</v>
@@ -9232,7 +8929,7 @@
         <v>20</v>
       </c>
       <c r="H147" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I147" t="n">
         <v>0.29</v>
@@ -9262,10 +8959,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="B148" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="C148" t="n">
         <v>2</v>
@@ -9280,10 +8977,10 @@
         <v>21</v>
       </c>
       <c r="G148" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H148" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I148" t="n">
         <v>0.025</v>
@@ -9313,10 +9010,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="B149" t="s">
-        <v>233</v>
+        <v>180</v>
       </c>
       <c r="C149" t="n">
         <v>3</v>
@@ -9334,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="H149" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I149" t="n">
         <v>0.14</v>
@@ -9364,10 +9061,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>239</v>
+        <v>182</v>
       </c>
       <c r="B150" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="C150" t="n">
         <v>3</v>
@@ -9382,10 +9079,10 @@
         <v>21</v>
       </c>
       <c r="G150" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H150" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I150" t="n">
         <v>0.15</v>
@@ -9415,10 +9112,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="B151" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -9436,7 +9133,7 @@
         <v>20</v>
       </c>
       <c r="H151" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I151" t="n">
         <v>0.085</v>
@@ -9466,10 +9163,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="B152" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="C152" t="n">
         <v>1</v>
@@ -9484,10 +9181,10 @@
         <v>21</v>
       </c>
       <c r="G152" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H152" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I152" t="n">
         <v>0.07</v>
@@ -9517,10 +9214,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>244</v>
+        <v>185</v>
       </c>
       <c r="B153" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="C153" t="n">
         <v>2</v>
@@ -9538,7 +9235,7 @@
         <v>20</v>
       </c>
       <c r="H153" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I153" t="n">
         <v>0.265</v>
@@ -9568,10 +9265,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>245</v>
+        <v>185</v>
       </c>
       <c r="B154" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="C154" t="n">
         <v>2</v>
@@ -9586,10 +9283,10 @@
         <v>21</v>
       </c>
       <c r="G154" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H154" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I154" t="n">
         <v>0.255</v>
@@ -9619,10 +9316,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>246</v>
+        <v>186</v>
       </c>
       <c r="B155" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
       <c r="C155" t="n">
         <v>3</v>
@@ -9637,10 +9334,10 @@
         <v>21</v>
       </c>
       <c r="G155" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H155" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I155" t="n">
         <v>0.21</v>
@@ -9670,10 +9367,10 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>247</v>
+        <v>187</v>
       </c>
       <c r="B156" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="C156" t="n">
         <v>1</v>
@@ -9691,7 +9388,7 @@
         <v>20</v>
       </c>
       <c r="H156" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I156" t="n">
         <v>0.185</v>
@@ -9721,10 +9418,10 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>249</v>
+        <v>187</v>
       </c>
       <c r="B157" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -9739,10 +9436,10 @@
         <v>21</v>
       </c>
       <c r="G157" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H157" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I157" t="n">
         <v>0.255</v>
@@ -9772,10 +9469,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>251</v>
+        <v>189</v>
       </c>
       <c r="B158" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="C158" t="n">
         <v>2</v>
@@ -9793,7 +9490,7 @@
         <v>20</v>
       </c>
       <c r="H158" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I158" t="n">
         <v>0.145</v>
@@ -9823,10 +9520,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>252</v>
+        <v>189</v>
       </c>
       <c r="B159" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="C159" t="n">
         <v>2</v>
@@ -9841,10 +9538,10 @@
         <v>21</v>
       </c>
       <c r="G159" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H159" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I159" t="n">
         <v>0.155</v>
@@ -9874,10 +9571,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>253</v>
+        <v>190</v>
       </c>
       <c r="B160" t="s">
-        <v>248</v>
+        <v>188</v>
       </c>
       <c r="C160" t="n">
         <v>3</v>
@@ -9895,7 +9592,7 @@
         <v>20</v>
       </c>
       <c r="H160" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I160" t="n">
         <v>0.165</v>
@@ -9925,10 +9622,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="B161" t="s">
-        <v>250</v>
+        <v>188</v>
       </c>
       <c r="C161" t="n">
         <v>3</v>
@@ -9943,10 +9640,10 @@
         <v>21</v>
       </c>
       <c r="G161" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H161" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I161" t="n">
         <v>0.11</v>
@@ -9976,10 +9673,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="B162" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -9997,7 +9694,7 @@
         <v>20</v>
       </c>
       <c r="H162" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I162" t="n">
         <v>0.125</v>
@@ -10027,10 +9724,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>257</v>
+        <v>191</v>
       </c>
       <c r="B163" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -10045,10 +9742,10 @@
         <v>21</v>
       </c>
       <c r="G163" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H163" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I163" t="n">
         <v>0.12</v>
@@ -10078,10 +9775,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>259</v>
+        <v>193</v>
       </c>
       <c r="B164" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="C164" t="n">
         <v>2</v>
@@ -10099,7 +9796,7 @@
         <v>20</v>
       </c>
       <c r="H164" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I164" t="n">
         <v>0.19</v>
@@ -10129,10 +9826,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="C165" t="n">
         <v>2</v>
@@ -10147,10 +9844,10 @@
         <v>21</v>
       </c>
       <c r="G165" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H165" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I165" t="n">
         <v>0.065</v>
@@ -10180,10 +9877,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>261</v>
+        <v>194</v>
       </c>
       <c r="B166" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="C166" t="n">
         <v>3</v>
@@ -10201,7 +9898,7 @@
         <v>20</v>
       </c>
       <c r="H166" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I166" t="n">
         <v>0.37</v>
@@ -10231,10 +9928,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>262</v>
+        <v>194</v>
       </c>
       <c r="B167" t="s">
-        <v>258</v>
+        <v>192</v>
       </c>
       <c r="C167" t="n">
         <v>3</v>
@@ -10249,10 +9946,10 @@
         <v>21</v>
       </c>
       <c r="G167" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H167" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I167" t="n">
         <v>0.05</v>
@@ -10282,10 +9979,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="B168" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
@@ -10303,7 +10000,7 @@
         <v>20</v>
       </c>
       <c r="H168" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I168" t="n">
         <v>0.24</v>
@@ -10333,10 +10030,10 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>265</v>
+        <v>195</v>
       </c>
       <c r="B169" t="s">
-        <v>266</v>
+        <v>196</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
@@ -10351,10 +10048,10 @@
         <v>21</v>
       </c>
       <c r="G169" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H169" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I169" t="n">
         <v>0.155</v>
@@ -10384,10 +10081,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>267</v>
+        <v>197</v>
       </c>
       <c r="B170" t="s">
-        <v>264</v>
+        <v>196</v>
       </c>
       <c r="C170" t="n">
         <v>2</v>
@@ -10405,7 +10102,7 @@
         <v>20</v>
       </c>
       <c r="H170" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I170" t="n">
         <v>0.26</v>
@@ -10435,10 +10132,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>268</v>
+        <v>198</v>
       </c>
       <c r="B171" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="C171" t="n">
         <v>1</v>
@@ -10456,7 +10153,7 @@
         <v>20</v>
       </c>
       <c r="H171" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I171" t="n">
         <v>0.375</v>
@@ -10486,10 +10183,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="B172" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="C172" t="n">
         <v>1</v>
@@ -10504,10 +10201,10 @@
         <v>21</v>
       </c>
       <c r="G172" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H172" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I172" t="n">
         <v>0.235</v>
@@ -10525,7 +10222,7 @@
       <c r="N172"/>
       <c r="O172"/>
       <c r="P172" t="s">
-        <v>272</v>
+        <v>200</v>
       </c>
       <c r="Q172" t="s">
         <v>78</v>
@@ -10533,10 +10230,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>273</v>
+        <v>201</v>
       </c>
       <c r="B173" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="C173" t="n">
         <v>2</v>
@@ -10554,7 +10251,7 @@
         <v>20</v>
       </c>
       <c r="H173" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I173" t="n">
         <v>0.165</v>
@@ -10584,10 +10281,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="B174" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="C174" t="n">
         <v>2</v>
@@ -10602,10 +10299,10 @@
         <v>21</v>
       </c>
       <c r="G174" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H174" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I174" t="n">
         <v>0.07</v>
@@ -10627,7 +10324,7 @@
         <v>0</v>
       </c>
       <c r="P174" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="Q174" t="s">
         <v>78</v>
@@ -10635,10 +10332,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="B175" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="C175" t="n">
         <v>2</v>
@@ -10653,10 +10350,10 @@
         <v>21</v>
       </c>
       <c r="G175" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H175" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I175" t="n">
         <v>0.42</v>
@@ -10678,7 +10375,7 @@
         <v>0.35</v>
       </c>
       <c r="P175" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
       <c r="Q175" t="s">
         <v>78</v>
@@ -10686,10 +10383,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>276</v>
+        <v>203</v>
       </c>
       <c r="B176" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="C176" t="n">
         <v>3</v>
@@ -10707,7 +10404,7 @@
         <v>20</v>
       </c>
       <c r="H176" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I176" t="n">
         <v>0.165</v>
@@ -10737,10 +10434,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>277</v>
+        <v>203</v>
       </c>
       <c r="B177" t="s">
-        <v>271</v>
+        <v>199</v>
       </c>
       <c r="C177" t="n">
         <v>3</v>
@@ -10755,10 +10452,10 @@
         <v>21</v>
       </c>
       <c r="G177" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H177" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I177" t="n">
         <v>0.105</v>
@@ -10782,7 +10479,7 @@
         <v>0</v>
       </c>
       <c r="P177" t="s">
-        <v>278</v>
+        <v>204</v>
       </c>
       <c r="Q177" t="s">
         <v>78</v>
@@ -10790,10 +10487,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>279</v>
+        <v>205</v>
       </c>
       <c r="B178" t="s">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
@@ -10811,7 +10508,7 @@
         <v>20</v>
       </c>
       <c r="H178" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I178" t="n">
         <v>0.215</v>
@@ -10841,10 +10538,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>282</v>
+        <v>208</v>
       </c>
       <c r="B179" t="s">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="C179" t="n">
         <v>2</v>
@@ -10862,7 +10559,7 @@
         <v>20</v>
       </c>
       <c r="H179" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I179" t="n">
         <v>0.33</v>
@@ -10892,10 +10589,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>283</v>
+        <v>209</v>
       </c>
       <c r="B180" t="s">
-        <v>280</v>
+        <v>206</v>
       </c>
       <c r="C180" t="n">
         <v>3</v>
@@ -10913,7 +10610,7 @@
         <v>20</v>
       </c>
       <c r="H180" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I180" t="n">
         <v>0.33</v>
@@ -10943,10 +10640,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>284</v>
+        <v>210</v>
       </c>
       <c r="B181" t="s">
-        <v>285</v>
+        <v>211</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
@@ -10964,7 +10661,7 @@
         <v>20</v>
       </c>
       <c r="H181" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I181" t="n">
         <v>0.26</v>
@@ -10994,10 +10691,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>286</v>
+        <v>212</v>
       </c>
       <c r="B182" t="s">
-        <v>285</v>
+        <v>211</v>
       </c>
       <c r="C182" t="n">
         <v>2</v>
@@ -11015,7 +10712,7 @@
         <v>20</v>
       </c>
       <c r="H182" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I182" t="n">
         <v>0.215</v>
@@ -11045,10 +10742,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>287</v>
+        <v>213</v>
       </c>
       <c r="B183" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
       <c r="C183" t="n">
         <v>1</v>
@@ -11066,7 +10763,7 @@
         <v>20</v>
       </c>
       <c r="H183" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I183" t="n">
         <v>0.2</v>
@@ -11096,10 +10793,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>289</v>
+        <v>215</v>
       </c>
       <c r="B184" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
       <c r="C184" t="n">
         <v>2</v>
@@ -11117,7 +10814,7 @@
         <v>20</v>
       </c>
       <c r="H184" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I184" t="n">
         <v>0.26</v>
@@ -11147,10 +10844,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>290</v>
+        <v>216</v>
       </c>
       <c r="B185" t="s">
-        <v>288</v>
+        <v>214</v>
       </c>
       <c r="C185" t="n">
         <v>3</v>
@@ -11168,7 +10865,7 @@
         <v>20</v>
       </c>
       <c r="H185" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I185" t="n">
         <v>0.175</v>
@@ -11198,10 +10895,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>291</v>
+        <v>217</v>
       </c>
       <c r="B186" t="s">
-        <v>292</v>
+        <v>218</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
@@ -11219,7 +10916,7 @@
         <v>20</v>
       </c>
       <c r="H186" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I186" t="n">
         <v>0.425</v>
@@ -11249,10 +10946,10 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>293</v>
+        <v>217</v>
       </c>
       <c r="B187" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="C187" t="n">
         <v>1</v>
@@ -11267,10 +10964,10 @@
         <v>21</v>
       </c>
       <c r="G187" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H187" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I187" t="n">
         <v>0.155</v>
@@ -11300,10 +10997,10 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="B188" t="s">
-        <v>292</v>
+        <v>218</v>
       </c>
       <c r="C188" t="n">
         <v>2</v>
@@ -11321,7 +11018,7 @@
         <v>20</v>
       </c>
       <c r="H188" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I188" t="n">
         <v>0.38</v>
@@ -11351,10 +11048,10 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>296</v>
+        <v>219</v>
       </c>
       <c r="B189" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="C189" t="n">
         <v>2</v>
@@ -11369,10 +11066,10 @@
         <v>21</v>
       </c>
       <c r="G189" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H189" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I189" t="n">
         <v>0.125</v>
@@ -11402,10 +11099,10 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>297</v>
+        <v>220</v>
       </c>
       <c r="B190" t="s">
-        <v>294</v>
+        <v>218</v>
       </c>
       <c r="C190" t="n">
         <v>3</v>
@@ -11420,10 +11117,10 @@
         <v>21</v>
       </c>
       <c r="G190" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H190" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I190" t="n">
         <v>0.175</v>
@@ -11453,10 +11150,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>298</v>
+        <v>221</v>
       </c>
       <c r="B191" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="C191" t="n">
         <v>1</v>
@@ -11474,7 +11171,7 @@
         <v>20</v>
       </c>
       <c r="H191" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I191" t="n">
         <v>0.345</v>
@@ -11504,10 +11201,10 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>300</v>
+        <v>223</v>
       </c>
       <c r="B192" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="C192" t="n">
         <v>2</v>
@@ -11525,7 +11222,7 @@
         <v>20</v>
       </c>
       <c r="H192" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I192" t="n">
         <v>0.245</v>
@@ -11555,10 +11252,10 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>301</v>
+        <v>223</v>
       </c>
       <c r="B193" t="s">
-        <v>302</v>
+        <v>222</v>
       </c>
       <c r="C193" t="n">
         <v>2</v>
@@ -11573,10 +11270,10 @@
         <v>21</v>
       </c>
       <c r="G193" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H193" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I193" t="n">
         <v>0.07</v>
@@ -11606,10 +11303,10 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>303</v>
+        <v>224</v>
       </c>
       <c r="B194" t="s">
-        <v>299</v>
+        <v>222</v>
       </c>
       <c r="C194" t="n">
         <v>3</v>
@@ -11627,7 +11324,7 @@
         <v>20</v>
       </c>
       <c r="H194" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I194" t="n">
         <v>0.375</v>
@@ -11657,10 +11354,10 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>304</v>
+        <v>224</v>
       </c>
       <c r="B195" t="s">
-        <v>302</v>
+        <v>222</v>
       </c>
       <c r="C195" t="n">
         <v>3</v>
@@ -11675,10 +11372,10 @@
         <v>21</v>
       </c>
       <c r="G195" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H195" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I195" t="n">
         <v>0.065</v>
@@ -11708,10 +11405,10 @@
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>305</v>
+        <v>225</v>
       </c>
       <c r="B196" t="s">
-        <v>302</v>
+        <v>222</v>
       </c>
       <c r="C196" t="n">
         <v>5</v>
@@ -11726,10 +11423,10 @@
         <v>21</v>
       </c>
       <c r="G196" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H196" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I196" t="n">
         <v>0.04</v>
@@ -11753,7 +11450,7 @@
         <v>0</v>
       </c>
       <c r="P196" t="s">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c r="Q196" t="s">
         <v>23</v>
@@ -11761,10 +11458,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>307</v>
+        <v>227</v>
       </c>
       <c r="B197" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -11782,7 +11479,7 @@
         <v>20</v>
       </c>
       <c r="H197" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I197" t="n">
         <v>0.395</v>
@@ -11812,10 +11509,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>309</v>
+        <v>229</v>
       </c>
       <c r="B198" t="s">
-        <v>308</v>
+        <v>228</v>
       </c>
       <c r="C198" t="n">
         <v>3</v>
@@ -11833,7 +11530,7 @@
         <v>20</v>
       </c>
       <c r="H198" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I198" t="n">
         <v>0.2</v>
@@ -11863,10 +11560,10 @@
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>310</v>
+        <v>230</v>
       </c>
       <c r="B199" t="s">
-        <v>311</v>
+        <v>231</v>
       </c>
       <c r="C199" t="n">
         <v>1</v>
@@ -11884,7 +11581,7 @@
         <v>20</v>
       </c>
       <c r="H199" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I199" t="n">
         <v>0.235</v>
@@ -11914,10 +11611,10 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>312</v>
+        <v>232</v>
       </c>
       <c r="B200" t="s">
-        <v>311</v>
+        <v>231</v>
       </c>
       <c r="C200" t="n">
         <v>2</v>
@@ -11935,7 +11632,7 @@
         <v>20</v>
       </c>
       <c r="H200" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I200" t="n">
         <v>0.085</v>
@@ -11965,10 +11662,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>313</v>
+        <v>232</v>
       </c>
       <c r="B201" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="C201" t="n">
         <v>2</v>
@@ -11983,10 +11680,10 @@
         <v>21</v>
       </c>
       <c r="G201" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H201" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I201" t="n">
         <v>0.175</v>
@@ -12016,10 +11713,10 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>315</v>
+        <v>233</v>
       </c>
       <c r="B202" t="s">
-        <v>311</v>
+        <v>231</v>
       </c>
       <c r="C202" t="n">
         <v>3</v>
@@ -12037,7 +11734,7 @@
         <v>20</v>
       </c>
       <c r="H202" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I202" t="n">
         <v>0.13</v>
@@ -12067,10 +11764,10 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>316</v>
+        <v>233</v>
       </c>
       <c r="B203" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="C203" t="n">
         <v>3</v>
@@ -12085,10 +11782,10 @@
         <v>21</v>
       </c>
       <c r="G203" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H203" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I203" t="n">
         <v>0.075</v>
@@ -12118,10 +11815,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>317</v>
+        <v>234</v>
       </c>
       <c r="B204" t="s">
-        <v>314</v>
+        <v>231</v>
       </c>
       <c r="C204" t="n">
         <v>4</v>
@@ -12136,10 +11833,10 @@
         <v>21</v>
       </c>
       <c r="G204" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H204" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I204" t="n">
         <v>0.09</v>
@@ -12163,7 +11860,7 @@
         <v>0</v>
       </c>
       <c r="P204" t="s">
-        <v>306</v>
+        <v>226</v>
       </c>
       <c r="Q204" t="s">
         <v>23</v>
@@ -12171,10 +11868,10 @@
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>318</v>
+        <v>235</v>
       </c>
       <c r="B205" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="C205" t="n">
         <v>1</v>
@@ -12192,7 +11889,7 @@
         <v>20</v>
       </c>
       <c r="H205" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I205" t="n">
         <v>0.275</v>
@@ -12222,10 +11919,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>320</v>
+        <v>237</v>
       </c>
       <c r="B206" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="C206" t="n">
         <v>2</v>
@@ -12243,7 +11940,7 @@
         <v>20</v>
       </c>
       <c r="H206" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I206" t="n">
         <v>0.15</v>
@@ -12273,10 +11970,10 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>321</v>
+        <v>238</v>
       </c>
       <c r="B207" t="s">
-        <v>319</v>
+        <v>236</v>
       </c>
       <c r="C207" t="n">
         <v>3</v>
@@ -12294,7 +11991,7 @@
         <v>20</v>
       </c>
       <c r="H207" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I207" t="n">
         <v>0.215</v>
@@ -12324,10 +12021,10 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>322</v>
+        <v>239</v>
       </c>
       <c r="B208" t="s">
-        <v>323</v>
+        <v>240</v>
       </c>
       <c r="C208" t="n">
         <v>1</v>
@@ -12345,7 +12042,7 @@
         <v>20</v>
       </c>
       <c r="H208" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I208" t="n">
         <v>0.465</v>
@@ -12375,10 +12072,10 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>324</v>
+        <v>239</v>
       </c>
       <c r="B209" t="s">
-        <v>325</v>
+        <v>240</v>
       </c>
       <c r="C209" t="n">
         <v>1</v>
@@ -12393,10 +12090,10 @@
         <v>21</v>
       </c>
       <c r="G209" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H209" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I209" t="n">
         <v>0.035</v>
@@ -12426,10 +12123,10 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>326</v>
+        <v>241</v>
       </c>
       <c r="B210" t="s">
-        <v>327</v>
+        <v>242</v>
       </c>
       <c r="C210" t="n">
         <v>1</v>
@@ -12447,7 +12144,7 @@
         <v>20</v>
       </c>
       <c r="H210" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I210" t="n">
         <v>0.115</v>
@@ -12477,10 +12174,10 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>328</v>
+        <v>243</v>
       </c>
       <c r="B211" t="s">
-        <v>327</v>
+        <v>242</v>
       </c>
       <c r="C211" t="n">
         <v>2</v>
@@ -12498,7 +12195,7 @@
         <v>20</v>
       </c>
       <c r="H211" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I211" t="n">
         <v>0.19</v>
@@ -12528,10 +12225,10 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>329</v>
+        <v>243</v>
       </c>
       <c r="B212" t="s">
-        <v>330</v>
+        <v>242</v>
       </c>
       <c r="C212" t="n">
         <v>2</v>
@@ -12546,10 +12243,10 @@
         <v>21</v>
       </c>
       <c r="G212" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H212" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I212" t="n">
         <v>0.2</v>
@@ -12579,10 +12276,10 @@
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>331</v>
+        <v>244</v>
       </c>
       <c r="B213" t="s">
-        <v>327</v>
+        <v>242</v>
       </c>
       <c r="C213" t="n">
         <v>3</v>
@@ -12600,7 +12297,7 @@
         <v>20</v>
       </c>
       <c r="H213" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I213" t="n">
         <v>0.23</v>
@@ -12630,10 +12327,10 @@
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>332</v>
+        <v>244</v>
       </c>
       <c r="B214" t="s">
-        <v>330</v>
+        <v>242</v>
       </c>
       <c r="C214" t="n">
         <v>3</v>
@@ -12648,10 +12345,10 @@
         <v>21</v>
       </c>
       <c r="G214" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H214" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I214" t="n">
         <v>0.305</v>
@@ -12681,10 +12378,10 @@
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>333</v>
+        <v>245</v>
       </c>
       <c r="B215" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="C215" t="n">
         <v>1</v>
@@ -12702,7 +12399,7 @@
         <v>20</v>
       </c>
       <c r="H215" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I215" t="n">
         <v>0.25</v>
@@ -12732,10 +12429,10 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>335</v>
+        <v>247</v>
       </c>
       <c r="B216" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="C216" t="n">
         <v>2</v>
@@ -12753,7 +12450,7 @@
         <v>20</v>
       </c>
       <c r="H216" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I216" t="n">
         <v>0.285</v>
@@ -12783,10 +12480,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>336</v>
+        <v>248</v>
       </c>
       <c r="B217" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="C217" t="n">
         <v>3</v>
@@ -12804,7 +12501,7 @@
         <v>20</v>
       </c>
       <c r="H217" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I217" t="n">
         <v>0.17</v>
@@ -12822,7 +12519,7 @@
       <c r="N217"/>
       <c r="O217"/>
       <c r="P217" t="s">
-        <v>337</v>
+        <v>249</v>
       </c>
       <c r="Q217" t="s">
         <v>78</v>
@@ -12830,10 +12527,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>338</v>
+        <v>250</v>
       </c>
       <c r="B218" t="s">
-        <v>334</v>
+        <v>246</v>
       </c>
       <c r="C218" t="n">
         <v>5</v>
@@ -12851,7 +12548,7 @@
         <v>20</v>
       </c>
       <c r="H218" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I218" t="n">
         <v>0.155</v>
@@ -12881,10 +12578,10 @@
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>339</v>
+        <v>251</v>
       </c>
       <c r="B219" t="s">
-        <v>340</v>
+        <v>252</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
@@ -12902,7 +12599,7 @@
         <v>20</v>
       </c>
       <c r="H219" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I219" t="n">
         <v>0.265</v>
@@ -12932,10 +12629,10 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>341</v>
+        <v>251</v>
       </c>
       <c r="B220" t="s">
-        <v>342</v>
+        <v>252</v>
       </c>
       <c r="C220" t="n">
         <v>1</v>
@@ -12950,10 +12647,10 @@
         <v>21</v>
       </c>
       <c r="G220" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H220" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I220" t="n">
         <v>0.2</v>
@@ -12983,10 +12680,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>343</v>
+        <v>253</v>
       </c>
       <c r="B221" t="s">
-        <v>340</v>
+        <v>252</v>
       </c>
       <c r="C221" t="n">
         <v>2</v>
@@ -13004,7 +12701,7 @@
         <v>20</v>
       </c>
       <c r="H221" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I221" t="n">
         <v>0.34</v>
@@ -13034,10 +12731,10 @@
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>344</v>
+        <v>253</v>
       </c>
       <c r="B222" t="s">
-        <v>342</v>
+        <v>252</v>
       </c>
       <c r="C222" t="n">
         <v>2</v>
@@ -13052,10 +12749,10 @@
         <v>21</v>
       </c>
       <c r="G222" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H222" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I222" t="n">
         <v>0.175</v>
@@ -13085,10 +12782,10 @@
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>345</v>
+        <v>254</v>
       </c>
       <c r="B223" t="s">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="C223" t="n">
         <v>1</v>
@@ -13106,7 +12803,7 @@
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I223" t="n">
         <v>0.095</v>
@@ -13136,10 +12833,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>347</v>
+        <v>254</v>
       </c>
       <c r="B224" t="s">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="C224" t="n">
         <v>1</v>
@@ -13154,10 +12851,10 @@
         <v>21</v>
       </c>
       <c r="G224" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H224" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I224" t="n">
         <v>0.145</v>
@@ -13187,10 +12884,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>349</v>
+        <v>256</v>
       </c>
       <c r="B225" t="s">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="C225" t="n">
         <v>2</v>
@@ -13208,7 +12905,7 @@
         <v>20</v>
       </c>
       <c r="H225" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I225" t="n">
         <v>0.24</v>
@@ -13238,10 +12935,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>350</v>
+        <v>256</v>
       </c>
       <c r="B226" t="s">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="C226" t="n">
         <v>2</v>
@@ -13256,10 +12953,10 @@
         <v>21</v>
       </c>
       <c r="G226" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H226" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I226" t="n">
         <v>0.145</v>
@@ -13289,10 +12986,10 @@
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>351</v>
+        <v>257</v>
       </c>
       <c r="B227" t="s">
-        <v>346</v>
+        <v>255</v>
       </c>
       <c r="C227" t="n">
         <v>3</v>
@@ -13310,7 +13007,7 @@
         <v>20</v>
       </c>
       <c r="H227" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I227" t="n">
         <v>0.25</v>
@@ -13340,10 +13037,10 @@
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>352</v>
+        <v>257</v>
       </c>
       <c r="B228" t="s">
-        <v>348</v>
+        <v>255</v>
       </c>
       <c r="C228" t="n">
         <v>3</v>
@@ -13358,10 +13055,10 @@
         <v>21</v>
       </c>
       <c r="G228" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H228" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I228" t="n">
         <v>0.12</v>
@@ -13391,10 +13088,10 @@
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>353</v>
+        <v>258</v>
       </c>
       <c r="B229" t="s">
-        <v>354</v>
+        <v>259</v>
       </c>
       <c r="C229" t="n">
         <v>1</v>
@@ -13412,7 +13109,7 @@
         <v>20</v>
       </c>
       <c r="H229" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I229" t="n">
         <v>0.165</v>
@@ -13442,10 +13139,10 @@
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>355</v>
+        <v>258</v>
       </c>
       <c r="B230" t="s">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="C230" t="n">
         <v>1</v>
@@ -13460,10 +13157,10 @@
         <v>21</v>
       </c>
       <c r="G230" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H230" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I230" t="n">
         <v>0.125</v>
@@ -13493,10 +13190,10 @@
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>357</v>
+        <v>260</v>
       </c>
       <c r="B231" t="s">
-        <v>354</v>
+        <v>259</v>
       </c>
       <c r="C231" t="n">
         <v>2</v>
@@ -13514,7 +13211,7 @@
         <v>20</v>
       </c>
       <c r="H231" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I231" t="n">
         <v>0.11</v>
@@ -13544,10 +13241,10 @@
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>358</v>
+        <v>260</v>
       </c>
       <c r="B232" t="s">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="C232" t="n">
         <v>2</v>
@@ -13562,10 +13259,10 @@
         <v>21</v>
       </c>
       <c r="G232" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H232" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I232" t="n">
         <v>0.085</v>
@@ -13595,10 +13292,10 @@
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>359</v>
+        <v>261</v>
       </c>
       <c r="B233" t="s">
-        <v>354</v>
+        <v>259</v>
       </c>
       <c r="C233" t="n">
         <v>3</v>
@@ -13616,7 +13313,7 @@
         <v>20</v>
       </c>
       <c r="H233" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I233" t="n">
         <v>0.045</v>
@@ -13646,10 +13343,10 @@
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>360</v>
+        <v>261</v>
       </c>
       <c r="B234" t="s">
-        <v>356</v>
+        <v>259</v>
       </c>
       <c r="C234" t="n">
         <v>3</v>
@@ -13664,10 +13361,10 @@
         <v>21</v>
       </c>
       <c r="G234" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H234" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I234" t="n">
         <v>0.155</v>
@@ -13697,10 +13394,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>361</v>
+        <v>262</v>
       </c>
       <c r="B235" t="s">
-        <v>362</v>
+        <v>263</v>
       </c>
       <c r="C235" t="n">
         <v>1</v>
@@ -13718,7 +13415,7 @@
         <v>20</v>
       </c>
       <c r="H235" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I235" t="n">
         <v>0.18</v>
@@ -13748,10 +13445,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>363</v>
+        <v>262</v>
       </c>
       <c r="B236" t="s">
-        <v>364</v>
+        <v>263</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
@@ -13766,10 +13463,10 @@
         <v>21</v>
       </c>
       <c r="G236" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H236" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I236" t="n">
         <v>0.13</v>
@@ -13793,7 +13490,7 @@
         <v>0</v>
       </c>
       <c r="P236" t="s">
-        <v>365</v>
+        <v>264</v>
       </c>
       <c r="Q236" t="s">
         <v>23</v>
@@ -13801,10 +13498,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>366</v>
+        <v>265</v>
       </c>
       <c r="B237" t="s">
-        <v>362</v>
+        <v>263</v>
       </c>
       <c r="C237" t="n">
         <v>2</v>
@@ -13822,7 +13519,7 @@
         <v>20</v>
       </c>
       <c r="H237" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I237" t="n">
         <v>0.235</v>
@@ -13852,10 +13549,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>367</v>
+        <v>266</v>
       </c>
       <c r="B238" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="C238" t="n">
         <v>1</v>
@@ -13870,10 +13567,10 @@
         <v>21</v>
       </c>
       <c r="G238" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H238" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I238" t="n">
         <v>0.21</v>
@@ -13903,10 +13600,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>369</v>
+        <v>268</v>
       </c>
       <c r="B239" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="C239" t="n">
         <v>2</v>
@@ -13921,10 +13618,10 @@
         <v>21</v>
       </c>
       <c r="G239" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H239" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I239" t="n">
         <v>0.14</v>
@@ -13954,10 +13651,10 @@
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>370</v>
+        <v>269</v>
       </c>
       <c r="B240" t="s">
-        <v>368</v>
+        <v>267</v>
       </c>
       <c r="C240" t="n">
         <v>3</v>
@@ -13972,10 +13669,10 @@
         <v>21</v>
       </c>
       <c r="G240" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H240" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I240" t="n">
         <v>0.16</v>
@@ -14005,10 +13702,10 @@
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
       <c r="B241" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="C241" t="n">
         <v>1</v>
@@ -14023,10 +13720,10 @@
         <v>21</v>
       </c>
       <c r="G241" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H241" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I241" t="n">
         <v>0.355</v>
@@ -14050,7 +13747,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="s">
-        <v>373</v>
+        <v>272</v>
       </c>
       <c r="Q241" t="s">
         <v>78</v>
@@ -14058,16 +13755,16 @@
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>371</v>
+        <v>270</v>
       </c>
       <c r="B242" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="C242" t="n">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>374</v>
+        <v>273</v>
       </c>
       <c r="E242" t="s">
         <v>6</v>
@@ -14076,10 +13773,10 @@
         <v>21</v>
       </c>
       <c r="G242" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H242" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I242" t="n">
         <v>0.255</v>
@@ -14103,7 +13800,7 @@
         <v>-0.1</v>
       </c>
       <c r="P242" t="s">
-        <v>373</v>
+        <v>272</v>
       </c>
       <c r="Q242" t="s">
         <v>78</v>
@@ -14111,10 +13808,10 @@
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>375</v>
+        <v>274</v>
       </c>
       <c r="B243" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="C243" t="n">
         <v>4</v>
@@ -14129,10 +13826,10 @@
         <v>21</v>
       </c>
       <c r="G243" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H243" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I243" t="n">
         <v>0.14</v>
@@ -14162,10 +13859,10 @@
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>376</v>
+        <v>275</v>
       </c>
       <c r="B244" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="C244" t="n">
         <v>5</v>
@@ -14180,10 +13877,10 @@
         <v>21</v>
       </c>
       <c r="G244" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H244" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I244" t="n">
         <v>0.2</v>
@@ -14207,7 +13904,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>377</v>
+        <v>276</v>
       </c>
       <c r="Q244" t="s">
         <v>78</v>
@@ -14215,10 +13912,10 @@
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>378</v>
+        <v>277</v>
       </c>
       <c r="B245" t="s">
-        <v>372</v>
+        <v>271</v>
       </c>
       <c r="C245" t="n">
         <v>6</v>
@@ -14233,10 +13930,10 @@
         <v>21</v>
       </c>
       <c r="G245" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H245" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I245" t="n">
         <v>0.32</v>
@@ -14268,10 +13965,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>379</v>
+        <v>278</v>
       </c>
       <c r="B246" t="s">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="C246" t="n">
         <v>1</v>
@@ -14286,10 +13983,10 @@
         <v>21</v>
       </c>
       <c r="G246" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H246" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I246" t="n">
         <v>0.195</v>
@@ -14319,10 +14016,10 @@
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>381</v>
+        <v>280</v>
       </c>
       <c r="B247" t="s">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="C247" t="n">
         <v>2</v>
@@ -14337,10 +14034,10 @@
         <v>21</v>
       </c>
       <c r="G247" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H247" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I247" t="n">
         <v>0.065</v>
@@ -14370,10 +14067,10 @@
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>382</v>
+        <v>281</v>
       </c>
       <c r="B248" t="s">
-        <v>380</v>
+        <v>279</v>
       </c>
       <c r="C248" t="n">
         <v>4</v>
@@ -14388,10 +14085,10 @@
         <v>21</v>
       </c>
       <c r="G248" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H248" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I248" t="n">
         <v>0.08</v>
@@ -14421,10 +14118,10 @@
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>383</v>
+        <v>282</v>
       </c>
       <c r="B249" t="s">
-        <v>384</v>
+        <v>283</v>
       </c>
       <c r="C249" t="n">
         <v>3</v>
@@ -14439,10 +14136,10 @@
         <v>21</v>
       </c>
       <c r="G249" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H249" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I249" t="n">
         <v>0.12</v>
@@ -14472,10 +14169,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="B250" t="s">
-        <v>384</v>
+        <v>283</v>
       </c>
       <c r="C250" t="n">
         <v>4</v>
@@ -14490,10 +14187,10 @@
         <v>21</v>
       </c>
       <c r="G250" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H250" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I250" t="n">
         <v>0.17</v>
@@ -14523,10 +14220,10 @@
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>386</v>
+        <v>285</v>
       </c>
       <c r="B251" t="s">
-        <v>384</v>
+        <v>283</v>
       </c>
       <c r="C251" t="n">
         <v>5</v>
@@ -14541,10 +14238,10 @@
         <v>21</v>
       </c>
       <c r="G251" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H251" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I251" t="n">
         <v>0.05</v>
@@ -14574,10 +14271,10 @@
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>387</v>
+        <v>286</v>
       </c>
       <c r="B252" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="C252" t="n">
         <v>1</v>
@@ -14592,10 +14289,10 @@
         <v>21</v>
       </c>
       <c r="G252" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H252" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I252" t="n">
         <v>0.185</v>
@@ -14625,10 +14322,10 @@
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>389</v>
+        <v>288</v>
       </c>
       <c r="B253" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="C253" t="n">
         <v>2</v>
@@ -14643,10 +14340,10 @@
         <v>21</v>
       </c>
       <c r="G253" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H253" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I253" t="n">
         <v>0.28</v>
@@ -14676,10 +14373,10 @@
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>390</v>
+        <v>289</v>
       </c>
       <c r="B254" t="s">
-        <v>388</v>
+        <v>287</v>
       </c>
       <c r="C254" t="n">
         <v>3</v>
@@ -14694,10 +14391,10 @@
         <v>21</v>
       </c>
       <c r="G254" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H254" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I254" t="n">
         <v>0.205</v>
@@ -14727,10 +14424,10 @@
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="B255" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="C255" t="n">
         <v>1</v>
@@ -14745,10 +14442,10 @@
         <v>21</v>
       </c>
       <c r="G255" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H255" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I255" t="n">
         <v>0.135</v>
@@ -14778,10 +14475,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>393</v>
+        <v>292</v>
       </c>
       <c r="B256" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="C256" t="n">
         <v>2</v>
@@ -14796,10 +14493,10 @@
         <v>21</v>
       </c>
       <c r="G256" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H256" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I256" t="n">
         <v>0.16</v>
@@ -14829,10 +14526,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>394</v>
+        <v>293</v>
       </c>
       <c r="B257" t="s">
-        <v>392</v>
+        <v>291</v>
       </c>
       <c r="C257" t="n">
         <v>3</v>
@@ -14847,10 +14544,10 @@
         <v>21</v>
       </c>
       <c r="G257" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H257" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I257" t="n">
         <v>0.135</v>
@@ -14874,7 +14571,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>395</v>
+        <v>294</v>
       </c>
       <c r="Q257" t="s">
         <v>78</v>
@@ -14882,10 +14579,10 @@
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>396</v>
+        <v>295</v>
       </c>
       <c r="B258" t="s">
-        <v>397</v>
+        <v>296</v>
       </c>
       <c r="C258" t="n">
         <v>1</v>
@@ -14933,10 +14630,10 @@
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>398</v>
+        <v>297</v>
       </c>
       <c r="B259" t="s">
-        <v>397</v>
+        <v>296</v>
       </c>
       <c r="C259" t="n">
         <v>2</v>
@@ -14984,10 +14681,10 @@
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>399</v>
+        <v>298</v>
       </c>
       <c r="B260" t="s">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="C260" t="n">
         <v>1</v>
@@ -15035,10 +14732,10 @@
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>401</v>
+        <v>300</v>
       </c>
       <c r="B261" t="s">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="C261" t="n">
         <v>2</v>
@@ -15086,10 +14783,10 @@
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>402</v>
+        <v>301</v>
       </c>
       <c r="B262" t="s">
-        <v>400</v>
+        <v>299</v>
       </c>
       <c r="C262" t="n">
         <v>3</v>
@@ -15137,10 +14834,10 @@
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>403</v>
+        <v>302</v>
       </c>
       <c r="B263" t="s">
-        <v>404</v>
+        <v>303</v>
       </c>
       <c r="C263" t="n">
         <v>1</v>
@@ -15188,10 +14885,10 @@
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>405</v>
+        <v>304</v>
       </c>
       <c r="B264" t="s">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="C264" t="n">
         <v>2</v>
@@ -15206,10 +14903,10 @@
         <v>21</v>
       </c>
       <c r="G264" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H264" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I264" t="n">
         <v>0.065</v>
@@ -15233,7 +14930,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
       <c r="Q264" t="s">
         <v>78</v>
@@ -15241,10 +14938,10 @@
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>408</v>
+        <v>307</v>
       </c>
       <c r="B265" t="s">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="C265" t="n">
         <v>4</v>
@@ -15259,10 +14956,10 @@
         <v>21</v>
       </c>
       <c r="G265" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H265" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I265" t="n">
         <v>0.045</v>
@@ -15292,10 +14989,10 @@
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>409</v>
+        <v>308</v>
       </c>
       <c r="B266" t="s">
-        <v>406</v>
+        <v>305</v>
       </c>
       <c r="C266" t="n">
         <v>5</v>
@@ -15310,10 +15007,10 @@
         <v>21</v>
       </c>
       <c r="G266" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H266" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I266" t="n">
         <v>0.045</v>
@@ -15331,7 +15028,7 @@
       <c r="N266"/>
       <c r="O266"/>
       <c r="P266" t="s">
-        <v>410</v>
+        <v>309</v>
       </c>
       <c r="Q266" t="s">
         <v>78</v>
@@ -15339,10 +15036,10 @@
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>411</v>
+        <v>310</v>
       </c>
       <c r="B267" t="s">
-        <v>412</v>
+        <v>311</v>
       </c>
       <c r="C267" t="n">
         <v>1</v>
@@ -15357,10 +15054,10 @@
         <v>21</v>
       </c>
       <c r="G267" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H267" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I267" t="n">
         <v>0.085</v>
@@ -15390,10 +15087,10 @@
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>413</v>
+        <v>312</v>
       </c>
       <c r="B268" t="s">
-        <v>412</v>
+        <v>311</v>
       </c>
       <c r="C268" t="n">
         <v>2</v>
@@ -15408,10 +15105,10 @@
         <v>21</v>
       </c>
       <c r="G268" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H268" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I268" t="n">
         <v>0.075</v>
@@ -15441,10 +15138,10 @@
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>414</v>
+        <v>313</v>
       </c>
       <c r="B269" t="s">
-        <v>412</v>
+        <v>311</v>
       </c>
       <c r="C269" t="n">
         <v>4</v>
@@ -15459,10 +15156,10 @@
         <v>21</v>
       </c>
       <c r="G269" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H269" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I269" t="n">
         <v>0.13</v>
@@ -15492,10 +15189,10 @@
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>415</v>
+        <v>314</v>
       </c>
       <c r="B270" t="s">
-        <v>416</v>
+        <v>315</v>
       </c>
       <c r="C270" t="n">
         <v>1</v>
@@ -15510,10 +15207,10 @@
         <v>21</v>
       </c>
       <c r="G270" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H270" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I270" t="n">
         <v>0.11</v>
@@ -15537,7 +15234,7 @@
         <v>0</v>
       </c>
       <c r="P270" t="s">
-        <v>417</v>
+        <v>316</v>
       </c>
       <c r="Q270" t="s">
         <v>78</v>
@@ -15545,10 +15242,10 @@
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>418</v>
+        <v>317</v>
       </c>
       <c r="B271" t="s">
-        <v>416</v>
+        <v>315</v>
       </c>
       <c r="C271" t="n">
         <v>2</v>
@@ -15563,10 +15260,10 @@
         <v>21</v>
       </c>
       <c r="G271" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H271" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I271" t="n">
         <v>0.095</v>
@@ -15596,10 +15293,10 @@
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>419</v>
+        <v>318</v>
       </c>
       <c r="B272" t="s">
-        <v>416</v>
+        <v>315</v>
       </c>
       <c r="C272" t="n">
         <v>3</v>
@@ -15614,10 +15311,10 @@
         <v>21</v>
       </c>
       <c r="G272" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H272" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I272" t="n">
         <v>0.075</v>
@@ -15641,7 +15338,7 @@
         <v>0</v>
       </c>
       <c r="P272" t="s">
-        <v>407</v>
+        <v>306</v>
       </c>
       <c r="Q272" t="s">
         <v>78</v>
@@ -15649,10 +15346,10 @@
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>420</v>
+        <v>319</v>
       </c>
       <c r="B273" t="s">
-        <v>421</v>
+        <v>320</v>
       </c>
       <c r="C273" t="n">
         <v>1</v>
@@ -15667,10 +15364,10 @@
         <v>21</v>
       </c>
       <c r="G273" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H273" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I273" t="n">
         <v>0.115</v>
@@ -15700,10 +15397,10 @@
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>422</v>
+        <v>321</v>
       </c>
       <c r="B274" t="s">
-        <v>421</v>
+        <v>320</v>
       </c>
       <c r="C274" t="n">
         <v>2</v>
@@ -15718,10 +15415,10 @@
         <v>21</v>
       </c>
       <c r="G274" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H274" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="I274" t="n">
         <v>0.205</v>
@@ -15751,10 +15448,10 @@
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="B275" t="s">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="C275" t="n">
         <v>1</v>
@@ -15769,10 +15466,10 @@
         <v>21</v>
       </c>
       <c r="G275" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H275" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I275" t="n">
         <v>0.03</v>
@@ -15802,10 +15499,10 @@
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>425</v>
+        <v>324</v>
       </c>
       <c r="B276" t="s">
-        <v>424</v>
+        <v>323</v>
       </c>
       <c r="C276" t="n">
         <v>3</v>
@@ -15820,10 +15517,10 @@
         <v>21</v>
       </c>
       <c r="G276" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="H276" t="s">
-        <v>281</v>
+        <v>207</v>
       </c>
       <c r="I276" t="n">
         <v>0.265</v>
@@ -15853,10 +15550,10 @@
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>426</v>
+        <v>325</v>
       </c>
       <c r="B277" t="s">
-        <v>427</v>
+        <v>326</v>
       </c>
       <c r="C277" t="n">
         <v>2</v>
@@ -15904,10 +15601,10 @@
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>428</v>
+        <v>327</v>
       </c>
       <c r="B278" t="s">
-        <v>427</v>
+        <v>326</v>
       </c>
       <c r="C278" t="n">
         <v>3</v>
@@ -15955,10 +15652,10 @@
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>429</v>
+        <v>328</v>
       </c>
       <c r="B279" t="s">
-        <v>430</v>
+        <v>329</v>
       </c>
       <c r="C279" t="n">
         <v>1</v>
@@ -16006,10 +15703,10 @@
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>431</v>
+        <v>330</v>
       </c>
       <c r="B280" t="s">
-        <v>430</v>
+        <v>329</v>
       </c>
       <c r="C280" t="n">
         <v>2</v>
@@ -16051,7 +15748,7 @@
         <v>0</v>
       </c>
       <c r="P280" t="s">
-        <v>432</v>
+        <v>331</v>
       </c>
       <c r="Q280" t="s">
         <v>23</v>
@@ -16059,10 +15756,10 @@
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>433</v>
+        <v>332</v>
       </c>
       <c r="B281" t="s">
-        <v>430</v>
+        <v>329</v>
       </c>
       <c r="C281" t="n">
         <v>3</v>
@@ -16095,7 +15792,7 @@
         <v>28.0172413793103</v>
       </c>
       <c r="M281" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N281" t="n">
         <v>0.065</v>
@@ -16110,10 +15807,10 @@
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>435</v>
+        <v>334</v>
       </c>
       <c r="B282" t="s">
-        <v>436</v>
+        <v>335</v>
       </c>
       <c r="C282" t="n">
         <v>1</v>
@@ -16161,10 +15858,10 @@
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>437</v>
+        <v>336</v>
       </c>
       <c r="B283" t="s">
-        <v>436</v>
+        <v>335</v>
       </c>
       <c r="C283" t="n">
         <v>2</v>
@@ -16197,7 +15894,7 @@
         <v>37.5854214123007</v>
       </c>
       <c r="M283" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N283" t="n">
         <v>0.165</v>
@@ -16212,10 +15909,10 @@
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>438</v>
+        <v>337</v>
       </c>
       <c r="B284" t="s">
-        <v>436</v>
+        <v>335</v>
       </c>
       <c r="C284" t="n">
         <v>3</v>
@@ -16263,10 +15960,10 @@
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>439</v>
+        <v>338</v>
       </c>
       <c r="B285" t="s">
-        <v>440</v>
+        <v>339</v>
       </c>
       <c r="C285" t="n">
         <v>1</v>
@@ -16314,10 +16011,10 @@
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>441</v>
+        <v>340</v>
       </c>
       <c r="B286" t="s">
-        <v>440</v>
+        <v>339</v>
       </c>
       <c r="C286" t="n">
         <v>2</v>
@@ -16365,10 +16062,10 @@
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="B287" t="s">
-        <v>440</v>
+        <v>339</v>
       </c>
       <c r="C287" t="n">
         <v>3</v>
@@ -16416,10 +16113,10 @@
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>443</v>
+        <v>342</v>
       </c>
       <c r="B288" t="s">
-        <v>444</v>
+        <v>343</v>
       </c>
       <c r="C288" t="n">
         <v>1</v>
@@ -16467,10 +16164,10 @@
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>445</v>
+        <v>344</v>
       </c>
       <c r="B289" t="s">
-        <v>444</v>
+        <v>343</v>
       </c>
       <c r="C289" t="n">
         <v>2</v>
@@ -16518,10 +16215,10 @@
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>446</v>
+        <v>345</v>
       </c>
       <c r="B290" t="s">
-        <v>444</v>
+        <v>343</v>
       </c>
       <c r="C290" t="n">
         <v>3</v>
@@ -16569,16 +16266,16 @@
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>447</v>
+        <v>346</v>
       </c>
       <c r="B291" t="s">
-        <v>448</v>
+        <v>347</v>
       </c>
       <c r="C291" t="n">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>449</v>
+        <v>348</v>
       </c>
       <c r="E291" t="s">
         <v>6</v>
@@ -16608,7 +16305,7 @@
       <c r="N291"/>
       <c r="O291"/>
       <c r="P291" t="s">
-        <v>450</v>
+        <v>349</v>
       </c>
       <c r="Q291" t="s">
         <v>23</v>
@@ -16616,10 +16313,10 @@
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>451</v>
+        <v>350</v>
       </c>
       <c r="B292" t="s">
-        <v>448</v>
+        <v>347</v>
       </c>
       <c r="C292" t="n">
         <v>2</v>
@@ -16652,7 +16349,7 @@
         <v>50</v>
       </c>
       <c r="M292" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N292" t="n">
         <v>0.13</v>
@@ -16667,16 +16364,16 @@
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>452</v>
+        <v>351</v>
       </c>
       <c r="B293" t="s">
-        <v>448</v>
+        <v>347</v>
       </c>
       <c r="C293" t="n">
         <v>3</v>
       </c>
       <c r="D293" t="s">
-        <v>374</v>
+        <v>273</v>
       </c>
       <c r="E293" t="s">
         <v>6</v>
@@ -16706,7 +16403,7 @@
       <c r="N293"/>
       <c r="O293"/>
       <c r="P293" t="s">
-        <v>453</v>
+        <v>352</v>
       </c>
       <c r="Q293" t="s">
         <v>23</v>
@@ -16714,10 +16411,10 @@
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>454</v>
+        <v>353</v>
       </c>
       <c r="B294" t="s">
-        <v>448</v>
+        <v>347</v>
       </c>
       <c r="C294" t="n">
         <v>4</v>
@@ -16765,10 +16462,10 @@
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>455</v>
+        <v>354</v>
       </c>
       <c r="B295" t="s">
-        <v>448</v>
+        <v>347</v>
       </c>
       <c r="C295" t="n">
         <v>5</v>
@@ -16816,10 +16513,10 @@
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>456</v>
+        <v>355</v>
       </c>
       <c r="B296" t="s">
-        <v>457</v>
+        <v>356</v>
       </c>
       <c r="C296" t="n">
         <v>1</v>
@@ -16859,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="P296" t="s">
-        <v>458</v>
+        <v>357</v>
       </c>
       <c r="Q296" t="s">
         <v>23</v>
@@ -16867,10 +16564,10 @@
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>459</v>
+        <v>358</v>
       </c>
       <c r="B297" t="s">
-        <v>457</v>
+        <v>356</v>
       </c>
       <c r="C297" t="n">
         <v>2</v>
@@ -16906,7 +16603,7 @@
       <c r="N297"/>
       <c r="O297"/>
       <c r="P297" t="s">
-        <v>460</v>
+        <v>359</v>
       </c>
       <c r="Q297" t="s">
         <v>23</v>
@@ -16914,10 +16611,10 @@
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>461</v>
+        <v>360</v>
       </c>
       <c r="B298" t="s">
-        <v>462</v>
+        <v>361</v>
       </c>
       <c r="C298" t="n">
         <v>1</v>
@@ -16965,10 +16662,10 @@
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>463</v>
+        <v>362</v>
       </c>
       <c r="B299" t="s">
-        <v>462</v>
+        <v>361</v>
       </c>
       <c r="C299" t="n">
         <v>2</v>
@@ -17016,10 +16713,10 @@
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>464</v>
+        <v>363</v>
       </c>
       <c r="B300" t="s">
-        <v>462</v>
+        <v>361</v>
       </c>
       <c r="C300" t="n">
         <v>3</v>
@@ -17052,7 +16749,7 @@
         <v>61.7977528089888</v>
       </c>
       <c r="M300" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N300" t="n">
         <v>0.11</v>
@@ -17067,10 +16764,10 @@
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>465</v>
+        <v>364</v>
       </c>
       <c r="B301" t="s">
-        <v>466</v>
+        <v>365</v>
       </c>
       <c r="C301" t="n">
         <v>1</v>
@@ -17106,7 +16803,7 @@
       <c r="N301"/>
       <c r="O301"/>
       <c r="P301" t="s">
-        <v>467</v>
+        <v>366</v>
       </c>
       <c r="Q301" t="s">
         <v>23</v>
@@ -17114,10 +16811,10 @@
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>468</v>
+        <v>367</v>
       </c>
       <c r="B302" t="s">
-        <v>466</v>
+        <v>365</v>
       </c>
       <c r="C302" t="n">
         <v>2</v>
@@ -17150,7 +16847,7 @@
         <v>51.1945392491468</v>
       </c>
       <c r="M302" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N302" t="n">
         <v>0.15</v>
@@ -17167,10 +16864,10 @@
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>469</v>
+        <v>368</v>
       </c>
       <c r="B303" t="s">
-        <v>466</v>
+        <v>365</v>
       </c>
       <c r="C303" t="n">
         <v>4</v>
@@ -17203,7 +16900,7 @@
         <v>53.4591194968554</v>
       </c>
       <c r="M303" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N303" t="n">
         <v>0.17</v>
@@ -17218,10 +16915,10 @@
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>470</v>
+        <v>369</v>
       </c>
       <c r="B304" t="s">
-        <v>466</v>
+        <v>365</v>
       </c>
       <c r="C304" t="n">
         <v>5</v>
@@ -17254,7 +16951,7 @@
         <v>72.9166666666667</v>
       </c>
       <c r="M304" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N304" t="n">
         <v>0.195</v>
@@ -17263,7 +16960,7 @@
         <v>0.015</v>
       </c>
       <c r="P304" t="s">
-        <v>471</v>
+        <v>370</v>
       </c>
       <c r="Q304" t="s">
         <v>23</v>
@@ -17271,16 +16968,16 @@
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>470</v>
+        <v>369</v>
       </c>
       <c r="B305" t="s">
-        <v>466</v>
+        <v>365</v>
       </c>
       <c r="C305" t="n">
         <v>5</v>
       </c>
       <c r="D305" t="s">
-        <v>472</v>
+        <v>371</v>
       </c>
       <c r="E305" t="s">
         <v>6</v>
@@ -17307,7 +17004,7 @@
         <v>67.7083333333333</v>
       </c>
       <c r="M305" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N305" t="n">
         <v>0.195</v>
@@ -17316,7 +17013,7 @@
         <v>0</v>
       </c>
       <c r="P305" t="s">
-        <v>471</v>
+        <v>370</v>
       </c>
       <c r="Q305" t="s">
         <v>23</v>
@@ -17324,10 +17021,10 @@
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>473</v>
+        <v>372</v>
       </c>
       <c r="B306" t="s">
-        <v>474</v>
+        <v>373</v>
       </c>
       <c r="C306" t="n">
         <v>1</v>
@@ -17375,10 +17072,10 @@
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>475</v>
+        <v>374</v>
       </c>
       <c r="B307" t="s">
-        <v>474</v>
+        <v>373</v>
       </c>
       <c r="C307" t="n">
         <v>2</v>
@@ -17411,7 +17108,7 @@
         <v>124.365482233503</v>
       </c>
       <c r="M307" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N307" t="n">
         <v>0.245</v>
@@ -17426,10 +17123,10 @@
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>476</v>
+        <v>375</v>
       </c>
       <c r="B308" t="s">
-        <v>474</v>
+        <v>373</v>
       </c>
       <c r="C308" t="n">
         <v>3</v>
@@ -17462,7 +17159,7 @@
         <v>37.1024734982332</v>
       </c>
       <c r="M308" t="s">
-        <v>434</v>
+        <v>333</v>
       </c>
       <c r="N308" t="n">
         <v>0.105</v>
